--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_273_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_273_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.2881</v>
+        <v>11.5707</v>
       </c>
       <c r="E2" t="n">
-        <v>9.8605</v>
+        <v>9.109500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4276</v>
+        <v>2.4612</v>
       </c>
       <c r="G2" t="n">
         <v>11.2659</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.017</v>
+        <v>0.2996</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5375</v>
+        <v>0.7866</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5206</v>
+        <v>-0.487</v>
       </c>
       <c r="V2" t="n">
         <v>1.8608</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5909</v>
+        <v>4.3054</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7416</v>
+        <v>6.2881</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1508</v>
+        <v>-1.9827</v>
       </c>
       <c r="G3" t="n">
         <v>2.6313</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7569</v>
+        <v>-0.0424</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4086</v>
+        <v>0.1379</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3484</v>
+        <v>-0.1803</v>
       </c>
       <c r="V3" t="n">
         <v>0.7886</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5142</v>
+        <v>2.2384</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8133</v>
+        <v>4.4031</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2991</v>
+        <v>-2.1647</v>
       </c>
       <c r="G4" t="n">
         <v>0.6591</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3743</v>
+        <v>0.3499</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5975</v>
+        <v>-0.0077</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2232</v>
+        <v>0.3576</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3943</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3317</v>
+        <v>2.1971</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1839</v>
+        <v>4.6125</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8522</v>
+        <v>-2.4153</v>
       </c>
       <c r="G5" t="n">
         <v>4.4777</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0584</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0351</v>
+        <v>0.3934</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0233</v>
+        <v>0.4136</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5361</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>G. LAVI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8143</v>
+        <v>0.483</v>
       </c>
       <c r="E6" t="n">
-        <v>0.823</v>
+        <v>-0.4336</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.9166</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2949</v>
+        <v>-1.0287</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0578</v>
+        <v>-1.2461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7629</v>
+        <v>0.2174</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2416</v>
+        <v>-0.6067</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8942</v>
+        <v>-1.0349</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6526</v>
+        <v>0.4282</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0533</v>
+        <v>-0.422</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1636</v>
+        <v>-0.2112</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1103</v>
+        <v>-0.2108</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.3519</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5272</v>
+        <v>0.1731</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3686</v>
+        <v>0.1788</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. LAVI</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0037</v>
+        <v>0.4088</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9801</v>
+        <v>0.8544</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9838</v>
+        <v>-0.4456</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0287</v>
+        <v>0.2949</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2461</v>
+        <v>1.0578</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2174</v>
+        <v>-0.7629</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6067</v>
+        <v>0.2416</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0349</v>
+        <v>0.8942</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4282</v>
+        <v>-0.6526</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.422</v>
+        <v>0.0533</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2112</v>
+        <v>0.1636</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2108</v>
+        <v>-0.1103</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1274</v>
+        <v>0.4903</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>0.5586</v>
       </c>
       <c r="U7" t="n">
-        <v>0.246</v>
+        <v>-0.0683</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.524</v>
+        <v>-0.1297</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.4994</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1681</v>
+        <v>0.3697</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5995</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3075</v>
+        <v>0.7018</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4129</v>
+        <v>0.6056</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1054</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4466</v>
+        <v>-1.8609</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.55</v>
+        <v>-1.065</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.7958</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9268</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4802</v>
+        <v>0.0659</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1246</v>
+        <v>0.6095</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6445</v>
+        <v>-0.5436</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5757</v>
+        <v>-3.269</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0774</v>
+        <v>-1.3002</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4983</v>
+        <v>-1.9688</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5575</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5875</v>
+        <v>0.8942</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0252</v>
+        <v>0.8024</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5623</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9792</v>
+        <v>-6.1797</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.4773</v>
+        <v>-6.5769</v>
       </c>
       <c r="F11" t="n">
-        <v>0.498</v>
+        <v>0.3972</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2309</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5706</v>
+        <v>0.2289</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0455</v>
+        <v>-0.1452</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4749</v>
+        <v>0.3741</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3943</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.017399999999999</v>
+        <v>9.764099999999997</v>
       </c>
       <c r="E12" t="n">
-        <v>14.6455</v>
+        <v>15.3925</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.628299999999999</v>
+        <v>-5.6282</v>
       </c>
       <c r="G12" t="n">
         <v>8.9855</v>
@@ -1390,13 +1390,13 @@
         <v>16.2368</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4003</v>
+        <v>4.1471</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1673</v>
+        <v>3.9142</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2328</v>
+        <v>0.2329</v>
       </c>
       <c r="V12" t="n">
         <v>0.1106999999999998</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9303</v>
+        <v>5.8568</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1747</v>
+        <v>5.0004</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7556</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>8.0382</v>
@@ -1468,13 +1468,13 @@
         <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5564</v>
+        <v>-0.63</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1044</v>
+        <v>-0.2787</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.452</v>
+        <v>-0.3512</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2636</v>
+        <v>2.3245</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4723</v>
+        <v>4.298</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2087</v>
+        <v>-1.9734</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9169</v>
@@ -1546,13 +1546,13 @@
         <v>3.0154</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.907</v>
+        <v>-0.8461</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2538</v>
+        <v>-0.4281</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6532</v>
+        <v>-0.418</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4887</v>
+        <v>-0.7645</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7906</v>
+        <v>2.3998</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2793</v>
+        <v>-3.1643</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.4551</v>
+        <v>-0.2022</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1227</v>
+        <v>0.1357</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.3324</v>
+        <v>-0.3379</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2499</v>
+        <v>3.9969</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6548</v>
+        <v>0.39</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4049</v>
+        <v>3.6069</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.2052</v>
+        <v>-4.1991</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5321</v>
+        <v>-0.2543</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.7373</v>
+        <v>-3.9448</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0618</v>
+        <v>-0.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0.543</v>
+        <v>-0.0431</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5188</v>
+        <v>-0.3569</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6468</v>
+        <v>-0.3943</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4975</v>
+        <v>-0.3943</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6057</v>
+        <v>-1.0993</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5058</v>
+        <v>1.0001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9001</v>
+        <v>-2.0994</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.656</v>
+        <v>3.3021</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4525</v>
+        <v>0.4081</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.1084</v>
+        <v>2.894</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.8519</v>
+        <v>7.4334</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3599</v>
+        <v>0.4341</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.2118</v>
+        <v>6.9993</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.804</v>
+        <v>-4.1313</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0926</v>
+        <v>-0.026</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8966</v>
+        <v>-4.1053</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5685</v>
+        <v>-0.5975</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3462</v>
+        <v>0.0123</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2223</v>
+        <v>-0.6097</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="X16" t="n">
         <v>-0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.27</v>
+        <v>-1.1447</v>
       </c>
       <c r="E17" t="n">
-        <v>1.928</v>
+        <v>-1.9776</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.1979</v>
+        <v>0.8329</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2022</v>
+        <v>-2.656</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1357</v>
+        <v>0.4525</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3379</v>
+        <v>-3.1084</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9969</v>
+        <v>-1.8519</v>
       </c>
       <c r="K17" t="n">
-        <v>0.39</v>
+        <v>0.3599</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6069</v>
+        <v>-2.2118</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.1991</v>
+        <v>-0.804</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2543</v>
+        <v>0.0926</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.9448</v>
+        <v>-0.8966</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9054</v>
+        <v>0.0294</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5149</v>
+        <v>-0.1256</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3905</v>
+        <v>0.1551</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3943</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8171</v>
+        <v>-1.6498</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2685</v>
+        <v>1.2009</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5486</v>
+        <v>-2.8507</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.7467</v>
+        <v>-3.4551</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.8667</v>
+        <v>-0.1227</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8799</v>
+        <v>-3.3324</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.577</v>
+        <v>-0.2499</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.2763</v>
+        <v>-0.6548</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6993</v>
+        <v>0.4049</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1696</v>
+        <v>-3.2052</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5904</v>
+        <v>0.5321</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5792</v>
+        <v>-3.7373</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7852</v>
+        <v>-0.0993</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5558</v>
+        <v>-0.0468</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2293</v>
+        <v>-0.0525</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>-0.6468</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>1.4975</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9744</v>
+        <v>-1.7098</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5283</v>
+        <v>1.1367</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5027</v>
+        <v>-2.8465</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3021</v>
+        <v>-1.6744</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4081</v>
+        <v>0.5942</v>
       </c>
       <c r="I19" t="n">
-        <v>2.894</v>
+        <v>-2.2686</v>
       </c>
       <c r="J19" t="n">
-        <v>7.4334</v>
+        <v>0.0015</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4341</v>
+        <v>0.3228</v>
       </c>
       <c r="L19" t="n">
-        <v>6.9993</v>
+        <v>-0.3213</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.1313</v>
+        <v>-1.6759</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.026</v>
+        <v>0.2714</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.1053</v>
+        <v>-1.9473</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.0154</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7834</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4725</v>
+        <v>-0.4993</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4595</v>
+        <v>0.063</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.013</v>
+        <v>-0.5623</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6468</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.198</v>
+        <v>-2.4342</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7828000000000001</v>
+        <v>-0.772</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9809</v>
+        <v>-1.6622</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6744</v>
+        <v>-1.0902</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5942</v>
+        <v>0.5726</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2686</v>
+        <v>-1.6629</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0015</v>
+        <v>0.6786</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3228</v>
+        <v>0.605</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3213</v>
+        <v>0.0736</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6759</v>
+        <v>-1.7688</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2714</v>
+        <v>-0.0323</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9473</v>
+        <v>-1.7365</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9875</v>
+        <v>-0.344</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2908</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6967</v>
+        <v>-0.0532</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.367</v>
+        <v>-3.8552</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.772</v>
+        <v>-3.0378</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.595</v>
+        <v>-0.8174</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0902</v>
+        <v>-4.7467</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5726</v>
+        <v>-3.8667</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6629</v>
+        <v>-0.8799</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6786</v>
+        <v>-2.577</v>
       </c>
       <c r="K21" t="n">
-        <v>0.605</v>
+        <v>-3.2763</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>0.6993</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7688</v>
+        <v>-2.1696</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0323</v>
+        <v>-0.5904</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7365</v>
+        <v>-1.5792</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2768</v>
+        <v>0.747</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2908</v>
+        <v>0.7866</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0141</v>
+        <v>-0.0395</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4904</v>
+        <v>-4.5411</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5022</v>
+        <v>-3.6202</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9881</v>
+        <v>-0.9209000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-5.5844</v>
@@ -2170,13 +2170,13 @@
         <v>3.2473</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7099</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2363</v>
+        <v>0.1184</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9462</v>
+        <v>-0.879</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2836</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.017399999999999</v>
+        <v>-9.017299999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>5.6282</v>
+        <v>5.628299999999999</v>
       </c>
       <c r="F23" t="n">
         <v>-14.6455</v>
       </c>
       <c r="G23" t="n">
-        <v>-8.985600000000002</v>
+        <v>-8.9856</v>
       </c>
       <c r="H23" t="n">
         <v>1.7884</v>
@@ -2248,19 +2248,19 @@
         <v>19.716</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.399999999999999</v>
+        <v>-3.4004</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2328999999999999</v>
+        <v>-0.2328</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.1671</v>
+        <v>-3.1672</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1107</v>
       </c>
       <c r="W23" t="n">
-        <v>4.2091</v>
+        <v>4.209099999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-4.3199</v>
